--- a/New Unity Project/Assets/Data/Dialogues/1-1.xlsx
+++ b/New Unity Project/Assets/Data/Dialogues/1-1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17243\AppData\Local\Kingsoft\WPS Office\12.1.0.28043\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gamejam\taptapgamejam\New Unity Project\Assets\Data\Dialogues\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="38">
   <si>
     <t>标志</t>
   </si>
@@ -121,19 +121,19 @@
     <t>好了，来吧，把撬棍递给我。</t>
   </si>
   <si>
+    <t>【点击撬棍收入背包，打开背包后鼠标拖拽给老人。】</t>
+  </si>
+  <si>
+    <t>调查bgm</t>
+  </si>
+  <si>
     <t>END</t>
   </si>
   <si>
-    <t>操作提示：点击撬棍收入背包，打开背包后鼠标拖拽给老人。</t>
-  </si>
-  <si>
-    <t>调查bgm</t>
-  </si>
-  <si>
     <t>很好，有这个就好办多了。你能再帮我把石头搬上车吗？</t>
   </si>
   <si>
-    <t>操作提示：鼠标拖拽石块到推车上。</t>
+    <t>【鼠标拖拽石块到推车上。】</t>
   </si>
   <si>
     <t>谢谢你，纳菲，愿乌阿斯蒂尔吉护佑你。</t>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>索斯兰么？他……昨天出了门。去村里看看吧，也许有人知道。</t>
+  </si>
+  <si>
+    <t>【点击小路尽头的建筑，进入村庄。】</t>
   </si>
 </sst>
 </file>
@@ -769,7 +772,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -778,6 +781,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1304,7 +1310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="16.8888888888889" customWidth="1"/>
@@ -1453,8 +1459,6 @@
       <c r="B9" s="1">
         <v>8</v>
       </c>
-      <c r="C9"/>
-      <c r="D9"/>
       <c r="E9" t="s">
         <v>17</v>
       </c>
@@ -1503,7 +1507,6 @@
       <c r="C12" t="s">
         <v>20</v>
       </c>
-      <c r="D12"/>
       <c r="E12" t="s">
         <v>21</v>
       </c>
@@ -1543,7 +1546,6 @@
       <c r="C14" t="s">
         <v>20</v>
       </c>
-      <c r="D14"/>
       <c r="E14" t="s">
         <v>25</v>
       </c>
@@ -1562,7 +1564,6 @@
       <c r="C15" t="s">
         <v>20</v>
       </c>
-      <c r="D15"/>
       <c r="E15" t="s">
         <v>26</v>
       </c>
@@ -1581,7 +1582,6 @@
       <c r="C16" t="s">
         <v>20</v>
       </c>
-      <c r="D16"/>
       <c r="E16" t="s">
         <v>27</v>
       </c>
@@ -1600,7 +1600,6 @@
       <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="D17"/>
       <c r="E17" t="s">
         <v>28</v>
       </c>
@@ -1611,48 +1610,47 @@
     </row>
     <row r="18" ht="56.65" customHeight="1" spans="1:7">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1">
         <v>17</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="1">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="19" ht="56.65" customHeight="1" spans="1:7">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="1">
-        <v>19</v>
-      </c>
+      <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" ht="56.65" customHeight="1" spans="1:7">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1">
         <v>19</v>
       </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
       <c r="E20" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="F20" s="1">
+        <v>20</v>
+      </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" ht="56.65" customHeight="1" spans="1:7">
@@ -1662,44 +1660,27 @@
       <c r="B21" s="1">
         <v>20</v>
       </c>
-      <c r="C21" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21"/>
       <c r="E21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21" s="1">
         <v>21</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" ht="56.65" customHeight="1" spans="1:7">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1">
         <v>21</v>
       </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="1">
-        <v>22</v>
-      </c>
+      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
     <row r="23" ht="56.65" customHeight="1" spans="1:7">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B23" s="1">
         <v>22</v>
@@ -1707,12 +1688,77 @@
       <c r="C23" t="s">
         <v>20</v>
       </c>
-      <c r="D23"/>
       <c r="E23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="1">
+        <v>23</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" ht="56.65" customHeight="1" spans="1:7">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="1">
+        <v>24</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" ht="56.65" customHeight="1" spans="1:7">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+      <c r="F25" s="1">
+        <v>25</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" ht="15.6" spans="1:7">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" ht="15.6" spans="1:7">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="1">
+        <v>26</v>
+      </c>
+      <c r="F27" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
